--- a/output/quickfixclose11_all_markets_daily.xlsx
+++ b/output/quickfixclose11_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose11_all_markets_daily.xlsx
+++ b/output/quickfixclose11_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,21 +842,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -864,16 +864,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.55</v>
+        <v>5.49</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106551.18</v>
+        <v>105485.66</v>
       </c>
     </row>
     <row r="9">
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1031,11 +1031,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1076,11 +1076,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1211,11 +1211,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>
@@ -5286,22 +5286,39 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
       <c r="G51" t="n">
         <v>2.69</v>
       </c>
       <c r="H51" t="n">
         <v>2.665</v>
       </c>
+      <c r="J51" t="n">
+        <v>2.665</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N51" t="n">
         <v>106551.18</v>
       </c>
       <c r="O51" t="n">
-        <v>106551.18</v>
+        <v>105485.66</v>
       </c>
     </row>
     <row r="52">

--- a/output/quickfixclose11_all_markets_daily.xlsx
+++ b/output/quickfixclose11_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>42.9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1031,11 +1031,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1076,11 +1076,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1211,11 +1211,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4676,11 +4676,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4689,48 +4689,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>3</v>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="G40" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H40" t="n">
-        <v>0.006454</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.006454</v>
+        <v>4363.8</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N40" t="n">
-        <v>100000</v>
+        <v>118749.68</v>
       </c>
       <c r="O40" t="n">
-        <v>99000</v>
+        <v>118749.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -4743,25 +4726,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H41" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="J41" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -4788,7 +4771,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4797,25 +4780,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H42" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="J42" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -4829,10 +4812,10 @@
         <v>-1</v>
       </c>
       <c r="N42" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O42" t="n">
         <v>99000</v>
-      </c>
-      <c r="O42" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="43">
@@ -4842,7 +4825,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4851,42 +4834,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H43" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="J43" t="n">
-        <v>247.15</v>
+        <v>251.91</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>6.584</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>6.584</v>
+        <v>-1</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N43" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O43" t="n">
         <v>98010</v>
-      </c>
-      <c r="O43" t="n">
-        <v>104462.98</v>
       </c>
     </row>
     <row r="44">
@@ -4896,61 +4879,61 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H44" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="J44" t="n">
-        <v>234.36</v>
+        <v>247.15</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>-1</v>
+        <v>6.584</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>6.584</v>
       </c>
       <c r="N44" t="n">
+        <v>98010</v>
+      </c>
+      <c r="O44" t="n">
         <v>104462.98</v>
-      </c>
-      <c r="O44" t="n">
-        <v>103418.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4959,25 +4942,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H45" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4991,10 +4974,10 @@
         <v>-1</v>
       </c>
       <c r="N45" t="n">
-        <v>100000</v>
+        <v>104462.98</v>
       </c>
       <c r="O45" t="n">
-        <v>99000</v>
+        <v>103418.35</v>
       </c>
     </row>
     <row r="46">
@@ -5004,7 +4987,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5013,12 +4996,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5028,10 +5011,10 @@
         <v>5.7714</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="J46" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5045,10 +5028,10 @@
         <v>-1</v>
       </c>
       <c r="N46" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O46" t="n">
         <v>99000</v>
-      </c>
-      <c r="O46" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="47">
@@ -5058,7 +5041,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5067,42 +5050,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H47" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="J47" t="n">
-        <v>5.777</v>
+        <v>5.6774</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.8798</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>6.8798</v>
+        <v>-1</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N47" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O47" t="n">
         <v>98010</v>
-      </c>
-      <c r="O47" t="n">
-        <v>104752.91</v>
       </c>
     </row>
     <row r="48">
@@ -5112,61 +5095,61 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H48" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="J48" t="n">
-        <v>6.1481</v>
+        <v>5.777</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>-1</v>
+        <v>6.8798</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>6.8798</v>
       </c>
       <c r="N48" t="n">
+        <v>98010</v>
+      </c>
+      <c r="O48" t="n">
         <v>104752.91</v>
-      </c>
-      <c r="O48" t="n">
-        <v>103705.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5175,25 +5158,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H49" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="J49" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5207,10 +5190,10 @@
         <v>-1</v>
       </c>
       <c r="N49" t="n">
-        <v>100000</v>
+        <v>104752.91</v>
       </c>
       <c r="O49" t="n">
-        <v>99000</v>
+        <v>103705.38</v>
       </c>
     </row>
     <row r="50">
@@ -5220,7 +5203,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5229,42 +5212,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>3.305</v>
       </c>
       <c r="H50" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J50" t="n">
-        <v>2.916</v>
+        <v>3.354</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>7.6275</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>7.6275</v>
+        <v>-1</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N50" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O50" t="n">
         <v>99000</v>
-      </c>
-      <c r="O50" t="n">
-        <v>106551.18</v>
       </c>
     </row>
     <row r="51">
@@ -5274,61 +5257,61 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G51" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H51" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J51" t="n">
-        <v>2.665</v>
+        <v>2.916</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>-1</v>
+        <v>7.6275</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>7.6275</v>
       </c>
       <c r="N51" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O51" t="n">
         <v>106551.18</v>
-      </c>
-      <c r="O51" t="n">
-        <v>105485.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5337,25 +5320,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H52" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J52" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5369,10 +5352,10 @@
         <v>-1</v>
       </c>
       <c r="N52" t="n">
-        <v>100000</v>
+        <v>106551.18</v>
       </c>
       <c r="O52" t="n">
-        <v>99000</v>
+        <v>105485.66</v>
       </c>
     </row>
     <row r="53">
@@ -5382,7 +5365,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5391,96 +5374,96 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H53" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J53" t="n">
-        <v>1307.7</v>
+        <v>1343.4</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>18.5132</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>18.5132</v>
+        <v>-1</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N53" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O53" t="n">
         <v>99000</v>
-      </c>
-      <c r="O53" t="n">
-        <v>117328.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G54" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H54" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2113.7</v>
+        <v>1307.7</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1</v>
+        <v>18.5132</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>18.5132</v>
       </c>
       <c r="N54" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O54" t="n">
-        <v>99000</v>
+        <v>117328.03</v>
       </c>
     </row>
     <row r="55">
@@ -5490,34 +5473,34 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>2</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
       <c r="G55" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H55" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J55" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5531,10 +5514,10 @@
         <v>-1</v>
       </c>
       <c r="N55" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O55" t="n">
         <v>99000</v>
-      </c>
-      <c r="O55" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="56">
@@ -5544,7 +5527,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5553,25 +5536,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H56" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J56" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5585,47 +5568,47 @@
         <v>-1</v>
       </c>
       <c r="N56" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O56" t="n">
         <v>98010</v>
-      </c>
-      <c r="O56" t="n">
-        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>27907</v>
+        <v>1581.5</v>
       </c>
       <c r="H57" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="J57" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5639,20 +5622,20 @@
         <v>-1</v>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O57" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5661,48 +5644,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G58" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H58" t="n">
-        <v>7223.26</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7223.26</v>
+        <v>1798.4</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -5715,25 +5681,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H59" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="J59" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5756,7 +5722,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -5769,52 +5735,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G60" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H60" t="n">
-        <v>6988.83</v>
-      </c>
-      <c r="J60" t="n">
-        <v>7002</v>
+        <v>30074.01</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>-3.0482</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N60" t="n">
         <v>99000</v>
       </c>
       <c r="O60" t="n">
-        <v>95982.27</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5823,25 +5772,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H61" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="J61" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5855,20 +5804,20 @@
         <v>-1</v>
       </c>
       <c r="N61" t="n">
-        <v>95982.27</v>
+        <v>100000</v>
       </c>
       <c r="O61" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5877,42 +5826,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G62" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H62" t="n">
-        <v>6986.84</v>
-      </c>
-      <c r="J62" t="n">
-        <v>6986.84</v>
+        <v>7820.26</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N62" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
       <c r="O62" t="n">
-        <v>94072.22</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="63">
@@ -5922,34 +5854,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>6794.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H63" t="n">
-        <v>6770.77</v>
+        <v>6965.7</v>
       </c>
       <c r="J63" t="n">
-        <v>6769.03</v>
+        <v>6965.7</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5957,26 +5889,26 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="N63" t="n">
-        <v>94072.22</v>
+        <v>100000</v>
       </c>
       <c r="O63" t="n">
-        <v>93062.23</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5985,25 +5917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H64" t="n">
-        <v>88.001</v>
+        <v>6988.83</v>
       </c>
       <c r="J64" t="n">
-        <v>88.001</v>
+        <v>7002</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6011,53 +5943,53 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N64" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O64" t="n">
-        <v>99000</v>
+        <v>95982.27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H65" t="n">
-        <v>71.999</v>
+        <v>6992.85</v>
       </c>
       <c r="J65" t="n">
-        <v>71.999</v>
+        <v>6992.85</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6071,20 +6003,20 @@
         <v>-1</v>
       </c>
       <c r="N65" t="n">
-        <v>99000</v>
+        <v>95982.27</v>
       </c>
       <c r="O65" t="n">
-        <v>98010</v>
+        <v>95022.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6093,25 +6025,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H66" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="J66" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6125,47 +6057,47 @@
         <v>-1</v>
       </c>
       <c r="N66" t="n">
-        <v>100000</v>
+        <v>95022.45</v>
       </c>
       <c r="O66" t="n">
-        <v>99000</v>
+        <v>94072.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H67" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="J67" t="n">
-        <v>21.08</v>
+        <v>6769.03</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6173,22 +6105,22 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="N67" t="n">
-        <v>100000</v>
+        <v>94072.22</v>
       </c>
       <c r="O67" t="n">
-        <v>98944.44</v>
+        <v>93062.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6201,25 +6133,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6242,7 +6174,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6250,30 +6182,30 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6296,61 +6228,61 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8436</v>
+        <v>15.26</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8498</v>
+        <v>15.26</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N70" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O70" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6363,25 +6295,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H71" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="J71" t="n">
-        <v>116.79</v>
+        <v>21.08</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6389,26 +6321,26 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N71" t="n">
         <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>99000</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6417,25 +6349,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="J72" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6449,47 +6381,47 @@
         <v>-1</v>
       </c>
       <c r="N72" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O72" t="n">
         <v>99000</v>
-      </c>
-      <c r="O72" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="J73" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6503,74 +6435,74 @@
         <v>-1</v>
       </c>
       <c r="N73" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O73" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>99.376</v>
+        <v>0.8467</v>
       </c>
       <c r="H74" t="n">
-        <v>99.571</v>
+        <v>0.8436</v>
       </c>
       <c r="J74" t="n">
-        <v>99.571</v>
+        <v>0.8498</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O74" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6579,25 +6511,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>100.066</v>
+        <v>116.5</v>
       </c>
       <c r="H75" t="n">
-        <v>100.201</v>
+        <v>116.79</v>
       </c>
       <c r="J75" t="n">
-        <v>100.201</v>
+        <v>116.79</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6611,20 +6543,20 @@
         <v>-1</v>
       </c>
       <c r="N75" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6633,25 +6565,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76" t="n">
-        <v>100.066</v>
+        <v>118.02</v>
       </c>
       <c r="H76" t="n">
-        <v>100.361</v>
+        <v>118.16</v>
       </c>
       <c r="J76" t="n">
-        <v>100.361</v>
+        <v>118.16</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6665,10 +6597,10 @@
         <v>-1</v>
       </c>
       <c r="N76" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O76" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="77">
@@ -6678,34 +6610,34 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" t="n">
-        <v>100.621</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>100.911</v>
+        <v>97.569</v>
       </c>
       <c r="J77" t="n">
-        <v>100.911</v>
+        <v>97.569</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6719,10 +6651,10 @@
         <v>-1</v>
       </c>
       <c r="N77" t="n">
-        <v>96059.60000000001</v>
+        <v>100000</v>
       </c>
       <c r="O77" t="n">
-        <v>95099</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="78">
@@ -6732,7 +6664,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6741,42 +6673,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>11</v>
       </c>
       <c r="G78" t="n">
-        <v>101.411</v>
+        <v>99.376</v>
       </c>
       <c r="H78" t="n">
-        <v>101.526</v>
+        <v>99.571</v>
       </c>
       <c r="J78" t="n">
-        <v>101.04</v>
+        <v>99.571</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.2261</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>3.2261</v>
+        <v>-1</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>95099</v>
+        <v>99000</v>
       </c>
       <c r="O78" t="n">
-        <v>98166.98</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="79">
@@ -6786,7 +6718,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6795,35 +6727,52 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H79" t="n">
-        <v>101.491</v>
+        <v>100.201</v>
+      </c>
+      <c r="J79" t="n">
+        <v>100.201</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N79" t="n">
-        <v>98166.98</v>
+        <v>98010</v>
       </c>
       <c r="O79" t="n">
-        <v>98166.98</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6832,25 +6781,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H80" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="J80" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6864,20 +6813,20 @@
         <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>100000</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>99000</v>
+        <v>96059.60000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6886,41 +6835,240 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>2</v>
       </c>
       <c r="G81" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H81" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="J81" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>96059.60000000001</v>
+      </c>
+      <c r="O81" t="n">
+        <v>95099</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>6</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>11</v>
+      </c>
+      <c r="G82" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H82" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J82" t="n">
+        <v>101.04</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>3.2261</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>3.2261</v>
+      </c>
+      <c r="N82" t="n">
+        <v>95099</v>
+      </c>
+      <c r="O82" t="n">
+        <v>98166.98</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H83" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>98166.98</v>
+      </c>
+      <c r="O83" t="n">
+        <v>98166.98</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H84" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J84" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O84" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" t="n">
         <v>130.16</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H85" t="n">
         <v>130.94</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J85" t="n">
         <v>139.27</v>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>stop</t>
         </is>
       </c>
-      <c r="L81" t="n">
+      <c r="L85" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="M81" s="5" t="n">
+      <c r="M85" s="5" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N85" t="n">
         <v>99000</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O85" t="n">
         <v>87437.31</v>
       </c>
     </row>

--- a/output/quickfixclose11_all_markets_daily.xlsx
+++ b/output/quickfixclose11_all_markets_daily.xlsx
@@ -554,20 +554,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -576,16 +576,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18.75</v>
+        <v>17.56</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>118749.68</v>
+        <v>117562.18</v>
       </c>
     </row>
     <row r="3">
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>50</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>25</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1031,11 +1031,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1076,11 +1076,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1211,11 +1211,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfixclose11 daily (exit = the close of price bar 11), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4692,22 +4692,39 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
       <c r="G40" t="n">
         <v>4305.3</v>
       </c>
       <c r="H40" t="n">
         <v>4363.8</v>
       </c>
+      <c r="J40" t="n">
+        <v>4363.8</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N40" t="n">
         <v>118749.68</v>
       </c>
       <c r="O40" t="n">
-        <v>118749.68</v>
+        <v>117562.18</v>
       </c>
     </row>
     <row r="41">
@@ -5199,11 +5216,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5212,42 +5229,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G50" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H50" t="n">
-        <v>3.354</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.354</v>
+        <v>6.7656</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N50" t="n">
-        <v>100000</v>
+        <v>103705.38</v>
       </c>
       <c r="O50" t="n">
-        <v>99000</v>
+        <v>103705.38</v>
       </c>
     </row>
     <row r="51">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5266,42 +5266,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>3.305</v>
       </c>
       <c r="H51" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J51" t="n">
-        <v>2.916</v>
+        <v>3.354</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>7.6275</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>7.6275</v>
+        <v>-1</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N51" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O51" t="n">
         <v>99000</v>
-      </c>
-      <c r="O51" t="n">
-        <v>106551.18</v>
       </c>
     </row>
     <row r="52">
@@ -5311,61 +5311,61 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H52" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J52" t="n">
-        <v>2.665</v>
+        <v>2.916</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>-1</v>
+        <v>7.6275</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>7.6275</v>
       </c>
       <c r="N52" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O52" t="n">
         <v>106551.18</v>
-      </c>
-      <c r="O52" t="n">
-        <v>105485.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5374,25 +5374,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G53" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H53" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J53" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         <v>-1</v>
       </c>
       <c r="N53" t="n">
-        <v>100000</v>
+        <v>106551.18</v>
       </c>
       <c r="O53" t="n">
-        <v>99000</v>
+        <v>105485.66</v>
       </c>
     </row>
     <row r="54">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5428,150 +5428,133 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H54" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J54" t="n">
-        <v>1307.7</v>
+        <v>1343.4</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>18.5132</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>18.5132</v>
+        <v>-1</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N54" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O54" t="n">
         <v>99000</v>
-      </c>
-      <c r="O54" t="n">
-        <v>117328.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G55" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H55" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J55" t="n">
-        <v>2113.7</v>
+        <v>1307.7</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>-1</v>
+        <v>18.5132</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>18.5132</v>
       </c>
       <c r="N55" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O55" t="n">
-        <v>99000</v>
+        <v>117328.03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H56" t="n">
-        <v>1621</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1621</v>
+        <v>1412.1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N56" t="n">
-        <v>99000</v>
+        <v>117328.03</v>
       </c>
       <c r="O56" t="n">
-        <v>98010</v>
+        <v>117328.03</v>
       </c>
     </row>
     <row r="57">
@@ -5581,34 +5564,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H57" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="J57" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5622,10 +5605,10 @@
         <v>-1</v>
       </c>
       <c r="N57" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O57" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="58">
@@ -5635,71 +5618,88 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1769.6</v>
+        <v>1641.5</v>
       </c>
       <c r="H58" t="n">
-        <v>1798.4</v>
+        <v>1621</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1621</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N58" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O58" t="n">
-        <v>97029.89999999999</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>27907</v>
+        <v>1581.5</v>
       </c>
       <c r="H59" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="J59" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5713,20 +5713,20 @@
         <v>-1</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O59" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H60" t="n">
-        <v>30074.01</v>
+        <v>1798.4</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -5772,25 +5772,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H61" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J61" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>7773</v>
+        <v>29892.8</v>
       </c>
       <c r="H62" t="n">
-        <v>7820.26</v>
+        <v>30074.01</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -5863,25 +5863,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>2</v>
       </c>
       <c r="G63" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H63" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="J63" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -5917,42 +5917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G64" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H64" t="n">
-        <v>6988.83</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7002</v>
+        <v>7820.26</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>-3.0482</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N64" t="n">
         <v>99000</v>
       </c>
       <c r="O64" t="n">
-        <v>95982.27</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="65">
@@ -5962,7 +5945,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -5971,25 +5954,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H65" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="J65" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6003,10 +5986,10 @@
         <v>-1</v>
       </c>
       <c r="N65" t="n">
-        <v>95982.27</v>
+        <v>100000</v>
       </c>
       <c r="O65" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="66">
@@ -6016,7 +5999,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6025,12 +6008,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -6040,10 +6023,10 @@
         <v>6982.4</v>
       </c>
       <c r="H66" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="J66" t="n">
-        <v>6986.84</v>
+        <v>7002</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6051,16 +6034,16 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N66" t="n">
-        <v>95022.45</v>
+        <v>99000</v>
       </c>
       <c r="O66" t="n">
-        <v>94072.22</v>
+        <v>95982.27</v>
       </c>
     </row>
     <row r="67">
@@ -6070,34 +6053,34 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H67" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="J67" t="n">
-        <v>6769.03</v>
+        <v>6992.85</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6105,26 +6088,26 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="N67" t="n">
-        <v>94072.22</v>
+        <v>95982.27</v>
       </c>
       <c r="O67" t="n">
-        <v>93062.23</v>
+        <v>95022.45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6133,25 +6116,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H68" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="J68" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6165,20 +6148,20 @@
         <v>-1</v>
       </c>
       <c r="N68" t="n">
-        <v>100000</v>
+        <v>95022.45</v>
       </c>
       <c r="O68" t="n">
-        <v>99000</v>
+        <v>94072.22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6187,25 +6170,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H69" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="J69" t="n">
-        <v>71.999</v>
+        <v>6769.03</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6213,22 +6196,22 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="N69" t="n">
-        <v>99000</v>
+        <v>94072.22</v>
       </c>
       <c r="O69" t="n">
-        <v>98010</v>
+        <v>93062.23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6241,25 +6224,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H70" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="J70" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6282,38 +6265,38 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="J71" t="n">
-        <v>21.08</v>
+        <v>71.999</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6321,22 +6304,22 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1.0556</v>
+        <v>-1</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1.0556</v>
+        <v>-1</v>
       </c>
       <c r="N71" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O71" t="n">
-        <v>98944.44</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6349,25 +6332,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6390,11 +6373,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -6403,25 +6386,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8658</v>
+        <v>21.08</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6429,16 +6412,16 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N73" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>98010</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="74">
@@ -6448,61 +6431,61 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N74" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6511,25 +6494,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="J75" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6543,70 +6526,70 @@
         <v>-1</v>
       </c>
       <c r="N75" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O75" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H76" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="J76" t="n">
-        <v>118.16</v>
+        <v>0.8498</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O76" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6614,30 +6597,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H77" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="J77" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6660,7 +6643,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6673,25 +6656,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H78" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="J78" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6718,34 +6701,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="J79" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6759,10 +6742,10 @@
         <v>-1</v>
       </c>
       <c r="N79" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="80">
@@ -6772,7 +6755,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6781,25 +6764,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H80" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="J80" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6813,10 +6796,10 @@
         <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O80" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="81">
@@ -6826,7 +6809,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6835,25 +6818,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H81" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="J81" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6867,10 +6850,10 @@
         <v>-1</v>
       </c>
       <c r="N81" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
       <c r="O81" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6880,7 +6863,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6889,42 +6872,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H82" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="J82" t="n">
-        <v>101.04</v>
+        <v>100.361</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>exit_close</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.2261</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>3.2261</v>
+        <v>-1</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N82" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O82" t="n">
-        <v>98166.98</v>
+        <v>96059.60000000001</v>
       </c>
     </row>
     <row r="83">
@@ -6934,7 +6917,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6943,35 +6926,52 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H83" t="n">
-        <v>101.491</v>
+        <v>100.911</v>
+      </c>
+      <c r="J83" t="n">
+        <v>100.911</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N83" t="n">
-        <v>98166.98</v>
+        <v>96059.60000000001</v>
       </c>
       <c r="O83" t="n">
-        <v>98166.98</v>
+        <v>95099</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -6980,95 +6980,186 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G84" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H84" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="J84" t="n">
-        <v>123.03</v>
+        <v>101.04</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>exit_close</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>-1</v>
+        <v>3.2261</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>3.2261</v>
       </c>
       <c r="N84" t="n">
-        <v>100000</v>
+        <v>95099</v>
       </c>
       <c r="O84" t="n">
-        <v>99000</v>
+        <v>98166.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>7</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H85" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>98166.98</v>
+      </c>
+      <c r="O85" t="n">
+        <v>98166.98</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H86" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J86" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O86" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
         <v>2</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="F87" t="n">
         <v>2</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G87" t="n">
         <v>130.16</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H87" t="n">
         <v>130.94</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J87" t="n">
         <v>139.27</v>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>stop</t>
         </is>
       </c>
-      <c r="L85" t="n">
+      <c r="L87" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="M85" s="5" t="n">
+      <c r="M87" s="5" t="n">
         <v>-11.6795</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N87" t="n">
         <v>99000</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O87" t="n">
         <v>87437.31</v>
       </c>
     </row>
